--- a/artfynd/A 25143-2023 artfynd.xlsx
+++ b/artfynd/A 25143-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25143-2023 artfynd.xlsx
+++ b/artfynd/A 25143-2023 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>121062765</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 25143-2023 artfynd.xlsx
+++ b/artfynd/A 25143-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2002,6 +2002,134 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124930316</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58191</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Falkstensmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>628364</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6646077</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Berg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Berg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25143-2023 artfynd.xlsx
+++ b/artfynd/A 25143-2023 artfynd.xlsx
@@ -2007,7 +2007,7 @@
         <v>124930316</v>
       </c>
       <c r="B13" t="n">
-        <v>58191</v>
+        <v>58305</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 25143-2023 artfynd.xlsx
+++ b/artfynd/A 25143-2023 artfynd.xlsx
@@ -2009,11 +2009,6 @@
       <c r="B13" t="n">
         <v>58305</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 25143-2023 artfynd.xlsx
+++ b/artfynd/A 25143-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57258</v>
+        <v>121062273</v>
       </c>
       <c r="B2" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenskvättan Ö, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628385.259137921</v>
+        <v>628483</v>
       </c>
       <c r="R2" t="n">
-        <v>6646000.975552761</v>
+        <v>6645921</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-04-29</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-04-29</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Artbestämning med DNA-analys (Palo  Merilä, 2003)</t>
+          <t>På avbarkad del av äldre granlåga i skog avverkningsanmäld av Mellanskog/Ulleråkers häradsallmänning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,75 +775,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Carlsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Carlsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SLU, FOMA, metamorfosförändringar hos grodyngel</t>
-        </is>
-      </c>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57247</v>
+        <v>63028190</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>larv</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenskvättan Ö, Upl</t>
+          <t>Falkstensmossen SO, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628385.259137921</v>
+        <v>628716</v>
       </c>
       <c r="R3" t="n">
-        <v>6646000.975552761</v>
+        <v>6646210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,27 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-06-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Artbestämning med DNA-analys (Palo &amp; Merilä, 2003)</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,69 +868,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>grovt granvindfälle i äldre barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunnar Carlsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunnar Carlsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1001108</v>
+        <v>81665380</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mosta, 1 km O, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628355.4981456453</v>
+        <v>628673</v>
       </c>
       <c r="R4" t="n">
-        <v>6645960.813421261</v>
+        <v>6646209</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,27 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-05-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1997-05-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inventering av mossfloran i Jumkil socken. Ruta 5</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,36 +970,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Glup</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>693289</v>
+        <v>1001108</v>
       </c>
       <c r="B5" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1089,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628355.4981456453</v>
+        <v>628355</v>
       </c>
       <c r="R5" t="n">
-        <v>6645960.813421261</v>
+        <v>6645961</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1122,19 +1054,9 @@
           <t>1997-05-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1997-05-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1171,15 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63028188</v>
+        <v>693289</v>
       </c>
       <c r="B6" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,42 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>2779</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Falkstensmossen SO, Upl</t>
+          <t>Mosta, 1 km O, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628755.8316135509</v>
+        <v>628355</v>
       </c>
       <c r="R6" t="n">
-        <v>6646196.457217468</v>
+        <v>6645961</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,22 +1158,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-05-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-05-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inventering av mossfloran i Jumkil socken. Ruta 5</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,33 +1182,28 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>torrgran i äldre blandskog</t>
+          <t>Glup</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63028189</v>
+        <v>63028188</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,34 +1211,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Falkstensmossen SO, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628733.1119226424</v>
+        <v>628756</v>
       </c>
       <c r="R7" t="n">
-        <v>6646185.131946291</v>
+        <v>6646196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,21 +1273,11 @@
           <t>2017-01-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-01-26</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1392,7 +1289,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>äldre blandskog</t>
+          <t>torrgran i äldre blandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1410,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63028190</v>
+        <v>63028187</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,34 +1318,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>102204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Falkstensmossen SO, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628715.6607169515</v>
+        <v>628727</v>
       </c>
       <c r="R8" t="n">
-        <v>6646210.107495412</v>
+        <v>6646200</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,21 +1380,11 @@
           <t>2017-01-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-01-26</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1509,7 +1396,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>grovt granvindfälle i äldre barrskog</t>
+          <t>grovgrenig gran i äldre blandskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1527,37 +1414,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63028187</v>
+        <v>63028191</v>
       </c>
       <c r="B9" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102204</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1572,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628726.5662129538</v>
+        <v>628712</v>
       </c>
       <c r="R9" t="n">
-        <v>6646199.952950069</v>
+        <v>6646218</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,21 +1487,11 @@
           <t>2017-01-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-01-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1631,7 +1503,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>grovgrenig gran i äldre blandskog</t>
+          <t>grov gran i äldre barrskog (enstaka gnag)</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1649,15 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63028191</v>
+        <v>121062765</v>
       </c>
       <c r="B10" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,42 +1532,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkstensmossen SO, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628712.3704711426</v>
+        <v>628332</v>
       </c>
       <c r="R10" t="n">
-        <v>6646218.018985308</v>
+        <v>6645888</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1724,22 +1595,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,74 +1621,80 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>grov gran i äldre barrskog (enstaka gnag)</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>81665380</v>
+        <v>124930316</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Falkstensmossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628672.9845478395</v>
+        <v>628364</v>
       </c>
       <c r="R11" t="n">
-        <v>6646209.123810504</v>
+        <v>6646077</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1841,22 +1718,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,27 +1748,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Berg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121062765</v>
+        <v>52762</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,46 +1771,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>larv</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Stenskvättan Ö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628332</v>
+        <v>628385</v>
       </c>
       <c r="R12" t="n">
-        <v>6645888</v>
+        <v>6646001</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1962,22 +1834,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2012-07-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2012-07-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Artbestämning med DNA-analys (Palo &amp; Merilä, 2003)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,22 +1859,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Gunnar Carlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Gunnar Carlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124930316</v>
+        <v>57258</v>
       </c>
       <c r="B13" t="n">
-        <v>58305</v>
+        <v>58815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,53 +1882,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>208250</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Falkstensmossen, Upl</t>
+          <t>Stenskvättan Ö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628364</v>
+        <v>628385</v>
       </c>
       <c r="R13" t="n">
-        <v>6646077</v>
+        <v>6646001</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2085,22 +1941,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2011-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2011-04-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Artbestämning med DNA-analys (Palo  Merilä, 2003)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2115,15 +1966,358 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Berg</t>
+          <t>Gunnar Carlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Berg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Gunnar Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SLU, FOMA, metamorfosförändringar hos grodyngel</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118496426</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>200 meter söder Falkstensmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>628369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6646186</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter med 7 blomställning i blockig nordvänd sluttning.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sven Kihlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sven Kihlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121062863</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>..., ..., Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>628253</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6645900</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>63028189</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Falkstensmossen SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>628733</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6646185</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
